--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93399</v>
+        <v>93402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93402</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93408</v>
+        <v>93410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93412</v>
+        <v>93414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93414</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93421</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>136603299</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
